--- a/sheets/국악이꽃피는나무/검수/안동역에서.xlsx
+++ b/sheets/국악이꽃피는나무/검수/안동역에서.xlsx
@@ -6545,28 +6545,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="57.97" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="64.69" customHeight="true">
+    <row r="3" ht="72.04" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="64.69" customHeight="true">
+    <row r="4" ht="72.04" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="64.69" customHeight="true">
+    <row r="5" ht="72.04" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="Q5" s="23"/>
     </row>
-    <row r="6" ht="64.69" customHeight="true">
+    <row r="6" ht="72.04" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="64.69" customHeight="true">
+    <row r="7" ht="72.04" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="64.69" customHeight="true">
+    <row r="8" ht="72.04" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="Q8" s="23"/>
     </row>
-    <row r="9" ht="64.69" customHeight="true">
+    <row r="9" ht="72.04" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="Q9" s="23"/>
     </row>
-    <row r="10" ht="64.69" customHeight="true">
+    <row r="10" ht="72.04" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="Q10" s="24"/>
     </row>
-    <row r="11" ht="64.69" customHeight="true">
+    <row r="11" ht="72.04" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="Q11" s="22"/>
     </row>
-    <row r="12" ht="64.69" customHeight="true">
+    <row r="12" ht="72.04" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="64.69" customHeight="true">
+    <row r="13" ht="72.04" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="64.69" customHeight="true">
+    <row r="14" ht="72.04" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="64.69" customHeight="true">
+    <row r="15" ht="72.04" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="64.69" customHeight="true">
+    <row r="16" ht="72.04" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="Q16" s="23"/>
     </row>
-    <row r="17" ht="64.69" customHeight="true">
+    <row r="17" ht="72.04" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="Q17" s="23"/>
     </row>
-    <row r="18" ht="64.69" customHeight="true">
+    <row r="18" ht="72.04" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
     <row r="19" ht="6.0" customHeight="true">
       <c r="A19" s="0"/>
     </row>
-    <row r="20" ht="57.97" customHeight="true">
+    <row r="20" ht="64.52" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="20" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
       <c r="P20" s="20"/>
       <c r="Q20" s="20"/>
     </row>
-    <row r="21" ht="64.69" customHeight="true">
+    <row r="21" ht="72.04" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="Q21" s="22"/>
     </row>
-    <row r="22" ht="64.69" customHeight="true">
+    <row r="22" ht="72.04" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="23"/>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="64.69" customHeight="true">
+    <row r="23" ht="72.04" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="23"/>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="64.69" customHeight="true">
+    <row r="24" ht="72.04" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="24"/>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="64.69" customHeight="true">
+    <row r="25" ht="72.04" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
@@ -7871,7 +7871,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="64.69" customHeight="true">
+    <row r="26" ht="72.04" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="23"/>
@@ -7907,7 +7907,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="64.69" customHeight="true">
+    <row r="27" ht="72.04" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="64.69" customHeight="true">
+    <row r="28" ht="72.04" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="64.69" customHeight="true">
+    <row r="29" ht="72.04" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="64.69" customHeight="true">
+    <row r="30" ht="72.04" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="23"/>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="64.69" customHeight="true">
+    <row r="31" ht="72.04" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="23"/>
@@ -8076,7 +8076,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="64.69" customHeight="true">
+    <row r="32" ht="72.04" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="24"/>
@@ -8107,7 +8107,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="64.69" customHeight="true">
+    <row r="33" ht="72.04" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="22"/>
@@ -8138,7 +8138,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="64.69" customHeight="true">
+    <row r="34" ht="72.04" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="23"/>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="Q34" s="23"/>
     </row>
-    <row r="35" ht="64.69" customHeight="true">
+    <row r="35" ht="72.04" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="23"/>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="Q35" s="23"/>
     </row>
-    <row r="36" ht="64.69" customHeight="true">
+    <row r="36" ht="72.04" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="24"/>
@@ -8226,7 +8226,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="69"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="18" max="16383" man="1"/>
   </rowBreaks>
